--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1497,40 +1497,120 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>30/08/2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brann</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M19" t="n">
+        <v>20</v>
+      </c>
+      <c r="N19" t="n">
+        <v>13</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>04/09/2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>18</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>

--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1613,22 +1613,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
+      </c>
+      <c r="N21" t="n">
+        <v>28</v>
+      </c>
+      <c r="O21" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>

--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1671,22 +1671,62 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20/09/2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M22" t="n">
+        <v>19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>7</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>

--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1729,22 +1729,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10/10/2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Rosenborg</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>8</v>
+      </c>
+      <c r="N23" t="n">
+        <v>21</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4</v>
+      </c>
+      <c r="P23" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>

--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1787,22 +1787,62 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18/10/2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M24" t="n">
+        <v>21</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>7</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>

--- a/new-stats/sandefjord-fotball.xlsx
+++ b/new-stats/sandefjord-fotball.xlsx
@@ -1845,22 +1845,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>25/10/2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sandefjord</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M25" t="n">
+        <v>18</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
